--- a/docs/templates/staff_directory_template.xlsx
+++ b/docs/templates/staff_directory_template.xlsx
@@ -189,20 +189,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StaffDirectory" displayName="StaffDirectory" ref="A1:K500" headerRowCount="1">
-  <autoFilter ref="A1:K500"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StaffDirectory" displayName="StaffDirectory" ref="A1:J500" headerRowCount="1">
+  <autoFilter ref="A1:J500"/>
+  <tableColumns count="10">
     <tableColumn id="1" name="First Name"/>
     <tableColumn id="2" name="Last Name"/>
     <tableColumn id="3" name="Preferred Name"/>
     <tableColumn id="4" name="Email"/>
     <tableColumn id="5" name="Position / Title"/>
     <tableColumn id="6" name="Classification"/>
-    <tableColumn id="7" name="Building"/>
-    <tableColumn id="8" name="Room"/>
-    <tableColumn id="9" name="Phone Ext."/>
-    <tableColumn id="10" name="OH Cert #"/>
-    <tableColumn id="11" name="HR Notes"/>
+    <tableColumn id="7" name="Room"/>
+    <tableColumn id="8" name="Phone Ext."/>
+    <tableColumn id="9" name="OH Cert #"/>
+    <tableColumn id="10" name="HR Notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -497,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -516,14 +515,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1. Upload this file to Google Drive and open it as a Google Sheet.</t>
+          <t>Each building keeps its OWN copy of this sheet. Nexus merges</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Right-click in Drive → Open with → Google Sheets. Save as a Sheet.)</t>
+          <t>every building's sheet into the staff directory nightly.</t>
         </is>
       </c>
     </row>
@@ -533,155 +532,151 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2. Share the resulting Sheet with your Nexus service account email</t>
+          <t>1. Make one copy of this file per building (e.g. 'Staff Directory — PHS',</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (same account you pasted into secrets/google_service_account.json)</t>
+          <t xml:space="preserve">   'Staff Directory — PES', etc.) and upload each to Google Drive.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   with Viewer access.</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2. Open each copy with Google Sheets (Drive → Right-click → Open with →</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>3. Copy the Sheet ID from its URL:</t>
+          <t xml:space="preserve">   Google Sheets → save as a Sheet).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     https://docs.google.com/spreadsheets/d/XXXXXXXXXXX/edit</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                       ^^^^^^^^^^^^</t>
+          <t>3. Share each Sheet with your Nexus service account email (the account</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   from secrets/google_service_account.json) — Viewer access is enough.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>4. Paste the Sheet ID into Nexus Settings → HR Google Sheets →</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   `sheet_id`. Nexus's HR sync job will poll the sheet nightly</t>
+          <t>4. Copy each Sheet ID from its URL:</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   and populate the staff directory.</t>
+          <t xml:space="preserve">     https://docs.google.com/spreadsheets/d/XXXXXXXXXXX/edit</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                       ^^^^^^^^^^^^</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>How this file is organized:</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>5. In Nexus → Settings → HR Google Sheets, click '+ Add Building' for</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>• Staff Directory tab</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   each building. Pick the building code, paste the Sheet ID. The</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Your HR team enters one row per staff member. Column headers in</t>
+          <t xml:space="preserve">   nightly HR sync will walk every building sheet.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    row 1 are matched by Nexus's HR sync — don't rename them. The</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    three example rows below the header are styled gray/italic and</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>How this file is organized:</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    can be deleted or overwritten with real data.</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>• Staff Directory tab</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>• Phone Directory tab</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Your HR team enters one row per staff member in THIS building.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Printable 8.5×11 portrait view of staff phone extensions,</t>
+          <t xml:space="preserve">    No 'Building' column — the Nexus config supplies that for every</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    sorted by building then last name. Pulls automatically from the</t>
+          <t xml:space="preserve">    row from this sheet. Column headers in row 1 are matched by Nexus,</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Staff Directory tab via SORT(FILTER()). To print: File →</t>
+          <t xml:space="preserve">    don't rename them. The three italic example rows can be deleted</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Print → Current sheet.</t>
+          <t xml:space="preserve">    or overwritten with real data.</t>
         </is>
       </c>
     </row>
@@ -689,47 +684,47 @@
       <c r="A31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Classification codes:</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>• Phone Directory tab</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Printable 8.5×11 portrait view of this building's staff phone</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Cert       — Certified teacher (OH licensed)</t>
+          <t xml:space="preserve">    extensions, sorted by last name. Pulls automatically from the</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Class      — Classified staff (custodial, cafeteria, aide, etc.)</t>
+          <t xml:space="preserve">    Staff Directory tab via SORT(FILTER()). To print: File → Print →</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Adm        — Administrator (principal, superintendent, etc.)</t>
+          <t xml:space="preserve">    Current sheet.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Adm-Class  — Administrator classified under union contract</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    xmpt       — Exempt / contracted (coaches, substitutes, etc.)</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Classification codes:</t>
         </is>
       </c>
     </row>
@@ -737,7 +732,45 @@
       <c r="A39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Cert       — Certified teacher (OH licensed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Class      — Classified staff (custodial, cafeteria, aide, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Adm        — Administrator (principal, superintendent, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Adm-Class  — Administrator classified under union contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    xmpt       — Exempt / contracted (coaches, substitutes, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Questions? See docs/DISTRICT_SETUP.pdf § HR Google Sheets.</t>
         </is>
@@ -754,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K500"/>
+  <dimension ref="A1:J500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -763,11 +796,10 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -803,25 +835,20 @@
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>Room</t>
         </is>
       </c>
       <c r="H1" s="6" t="inlineStr">
         <is>
-          <t>Room</t>
+          <t>Phone Ext.</t>
         </is>
       </c>
       <c r="I1" s="6" t="inlineStr">
         <is>
-          <t>Phone Ext.</t>
+          <t>OH Cert #</t>
         </is>
       </c>
       <c r="J1" s="6" t="inlineStr">
-        <is>
-          <t>OH Cert #</t>
-        </is>
-      </c>
-      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>HR Notes</t>
         </is>
@@ -856,25 +883,20 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>Elementary</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>3203</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr"/>
+      <c r="J2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -909,21 +931,16 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>High School</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>Shop</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
           <t>1500</t>
         </is>
       </c>
+      <c r="I3" s="7" t="inlineStr"/>
       <c r="J3" s="7" t="inlineStr"/>
-      <c r="K3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -952,19 +969,14 @@
           <t>Adm</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Central Office</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr"/>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr"/>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>former last name: Lopez</t>
         </is>
@@ -981,7 +993,6 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -994,7 +1005,6 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1007,7 +1017,6 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1020,7 +1029,6 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1033,7 +1041,6 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1046,7 +1053,6 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1059,7 +1065,6 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1072,7 +1077,6 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1085,7 +1089,6 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1098,7 +1101,6 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1111,7 +1113,6 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1124,7 +1125,6 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1137,7 +1137,6 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1150,7 +1149,6 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1163,7 +1161,6 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1176,7 +1173,6 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1189,7 +1185,6 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1202,7 +1197,6 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1215,7 +1209,6 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1228,7 +1221,6 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1241,7 +1233,6 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1254,7 +1245,6 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1267,7 +1257,6 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1280,7 +1269,6 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -1293,7 +1281,6 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -1306,7 +1293,6 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -1319,7 +1305,6 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -1332,7 +1317,6 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -1345,7 +1329,6 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -1358,7 +1341,6 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -1371,7 +1353,6 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -1384,7 +1365,6 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -1397,7 +1377,6 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -1410,7 +1389,6 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -1423,7 +1401,6 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -1436,7 +1413,6 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -1449,7 +1425,6 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -1462,7 +1437,6 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -1475,7 +1449,6 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -1488,7 +1461,6 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -1501,7 +1473,6 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -1514,7 +1485,6 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -1527,7 +1497,6 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -1540,7 +1509,6 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -1553,7 +1521,6 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -1566,7 +1533,6 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -1579,7 +1545,6 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -1592,7 +1557,6 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -1605,7 +1569,6 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -1618,7 +1581,6 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -1631,7 +1593,6 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -1644,7 +1605,6 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -1657,7 +1617,6 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -1670,7 +1629,6 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -1683,7 +1641,6 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -1696,7 +1653,6 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -1709,7 +1665,6 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -1722,7 +1677,6 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -1735,7 +1689,6 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -1748,7 +1701,6 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -1761,7 +1713,6 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -1774,7 +1725,6 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -1787,7 +1737,6 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -1800,7 +1749,6 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -1813,7 +1761,6 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -1826,7 +1773,6 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -1839,7 +1785,6 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -1852,7 +1797,6 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -1865,7 +1809,6 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -1878,7 +1821,6 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -1891,7 +1833,6 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -1904,7 +1845,6 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -1917,7 +1857,6 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -1930,7 +1869,6 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -1943,7 +1881,6 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -1956,7 +1893,6 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
@@ -1969,7 +1905,6 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
@@ -1982,7 +1917,6 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
@@ -1995,7 +1929,6 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
@@ -2008,7 +1941,6 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
@@ -2021,7 +1953,6 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
@@ -2034,7 +1965,6 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
@@ -2047,7 +1977,6 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
@@ -2060,7 +1989,6 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
@@ -2073,7 +2001,6 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
@@ -2086,7 +2013,6 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
@@ -2099,7 +2025,6 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
@@ -2112,7 +2037,6 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
@@ -2125,7 +2049,6 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
@@ -2138,7 +2061,6 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
@@ -2151,7 +2073,6 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
@@ -2164,7 +2085,6 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
@@ -2177,7 +2097,6 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
@@ -2190,7 +2109,6 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
@@ -2203,7 +2121,6 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
@@ -2216,7 +2133,6 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
@@ -2229,7 +2145,6 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
@@ -2242,7 +2157,6 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
@@ -2255,7 +2169,6 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
@@ -2268,7 +2181,6 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
@@ -2281,7 +2193,6 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
@@ -2294,7 +2205,6 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
@@ -2307,7 +2217,6 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
@@ -2320,7 +2229,6 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
@@ -2333,7 +2241,6 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
@@ -2346,7 +2253,6 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
@@ -2359,7 +2265,6 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
@@ -2372,7 +2277,6 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
@@ -2385,7 +2289,6 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
@@ -2398,7 +2301,6 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
@@ -2411,7 +2313,6 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
@@ -2424,7 +2325,6 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
@@ -2437,7 +2337,6 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
@@ -2450,7 +2349,6 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
@@ -2463,7 +2361,6 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
@@ -2476,7 +2373,6 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
@@ -2489,7 +2385,6 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
@@ -2502,7 +2397,6 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
@@ -2515,7 +2409,6 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
@@ -2528,7 +2421,6 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
@@ -2541,7 +2433,6 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
@@ -2554,7 +2445,6 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
@@ -2567,7 +2457,6 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
@@ -2580,7 +2469,6 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
@@ -2593,7 +2481,6 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
@@ -2606,7 +2493,6 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
@@ -2619,7 +2505,6 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
@@ -2632,7 +2517,6 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
@@ -2645,7 +2529,6 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
@@ -2658,7 +2541,6 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
@@ -2671,7 +2553,6 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
@@ -2684,7 +2565,6 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
@@ -2697,7 +2577,6 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
@@ -2710,7 +2589,6 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
@@ -2723,7 +2601,6 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
@@ -2736,7 +2613,6 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
@@ -2749,7 +2625,6 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
@@ -2762,7 +2637,6 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
@@ -2775,7 +2649,6 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
@@ -2788,7 +2661,6 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
@@ -2801,7 +2673,6 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
@@ -2814,7 +2685,6 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
@@ -2827,7 +2697,6 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
@@ -2840,7 +2709,6 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
@@ -2853,7 +2721,6 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
@@ -2866,7 +2733,6 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
@@ -2879,7 +2745,6 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
@@ -2892,7 +2757,6 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
@@ -2905,7 +2769,6 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
@@ -2918,7 +2781,6 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
@@ -2931,7 +2793,6 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
@@ -2944,7 +2805,6 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
@@ -2957,7 +2817,6 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
@@ -2970,7 +2829,6 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
@@ -2983,7 +2841,6 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
@@ -2996,7 +2853,6 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
@@ -3009,7 +2865,6 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -3022,7 +2877,6 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
@@ -3035,7 +2889,6 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
@@ -3048,7 +2901,6 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
@@ -3061,7 +2913,6 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
@@ -3074,7 +2925,6 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
@@ -3087,7 +2937,6 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
@@ -3100,7 +2949,6 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
@@ -3113,7 +2961,6 @@
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
@@ -3126,7 +2973,6 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
@@ -3139,7 +2985,6 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
@@ -3152,7 +2997,6 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
@@ -3165,7 +3009,6 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
@@ -3178,7 +3021,6 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
@@ -3191,7 +3033,6 @@
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
@@ -3204,7 +3045,6 @@
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
@@ -3217,7 +3057,6 @@
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
@@ -3230,7 +3069,6 @@
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr"/>
@@ -3243,7 +3081,6 @@
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
@@ -3256,7 +3093,6 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>
@@ -3269,7 +3105,6 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr"/>
@@ -3282,7 +3117,6 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
@@ -3295,7 +3129,6 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr"/>
@@ -3308,7 +3141,6 @@
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
@@ -3321,7 +3153,6 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr"/>
@@ -3334,7 +3165,6 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr"/>
@@ -3347,7 +3177,6 @@
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr"/>
@@ -3360,7 +3189,6 @@
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr"/>
@@ -3373,7 +3201,6 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr"/>
@@ -3386,7 +3213,6 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr"/>
@@ -3399,7 +3225,6 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr"/>
@@ -3412,7 +3237,6 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr"/>
@@ -3425,7 +3249,6 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
@@ -3438,7 +3261,6 @@
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr"/>
@@ -3451,7 +3273,6 @@
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr"/>
@@ -3464,7 +3285,6 @@
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr"/>
@@ -3477,7 +3297,6 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
@@ -3490,7 +3309,6 @@
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr"/>
@@ -3503,7 +3321,6 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr"/>
@@ -3516,7 +3333,6 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr"/>
@@ -3529,7 +3345,6 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr"/>
@@ -3542,7 +3357,6 @@
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
@@ -3555,7 +3369,6 @@
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr"/>
@@ -3568,7 +3381,6 @@
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr"/>
@@ -3581,7 +3393,6 @@
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr"/>
@@ -3594,7 +3405,6 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr"/>
@@ -3607,7 +3417,6 @@
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
@@ -3620,7 +3429,6 @@
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
@@ -3633,7 +3441,6 @@
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>
@@ -3646,7 +3453,6 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
@@ -3659,7 +3465,6 @@
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr"/>
@@ -3672,7 +3477,6 @@
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr"/>
@@ -3685,7 +3489,6 @@
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr"/>
@@ -3698,7 +3501,6 @@
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr"/>
@@ -3711,7 +3513,6 @@
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr"/>
@@ -3724,7 +3525,6 @@
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr"/>
@@ -3737,7 +3537,6 @@
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr"/>
@@ -3750,7 +3549,6 @@
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr"/>
@@ -3763,7 +3561,6 @@
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr"/>
@@ -3776,7 +3573,6 @@
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr"/>
@@ -3789,7 +3585,6 @@
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr"/>
@@ -3802,7 +3597,6 @@
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr"/>
@@ -3815,7 +3609,6 @@
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
-      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr"/>
@@ -3828,7 +3621,6 @@
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr"/>
@@ -3841,7 +3633,6 @@
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr"/>
@@ -3854,7 +3645,6 @@
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr"/>
@@ -3867,7 +3657,6 @@
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr"/>
@@ -3880,7 +3669,6 @@
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr"/>
@@ -3893,7 +3681,6 @@
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr"/>
@@ -3906,7 +3693,6 @@
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>
@@ -3919,7 +3705,6 @@
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr"/>
@@ -3932,7 +3717,6 @@
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr"/>
@@ -3945,7 +3729,6 @@
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr"/>
@@ -3958,7 +3741,6 @@
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr"/>
@@ -3971,7 +3753,6 @@
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr"/>
@@ -3984,7 +3765,6 @@
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr"/>
@@ -3997,7 +3777,6 @@
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr"/>
@@ -4010,7 +3789,6 @@
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr"/>
@@ -4023,7 +3801,6 @@
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr"/>
@@ -4036,7 +3813,6 @@
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr"/>
@@ -4049,7 +3825,6 @@
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr"/>
@@ -4062,7 +3837,6 @@
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr"/>
@@ -4075,7 +3849,6 @@
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr"/>
@@ -4088,7 +3861,6 @@
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr"/>
@@ -4101,7 +3873,6 @@
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr"/>
@@ -4114,7 +3885,6 @@
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr"/>
@@ -4127,7 +3897,6 @@
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr"/>
@@ -4140,7 +3909,6 @@
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr"/>
@@ -4153,7 +3921,6 @@
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr"/>
@@ -4166,7 +3933,6 @@
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr"/>
@@ -4179,7 +3945,6 @@
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr"/>
@@ -4192,7 +3957,6 @@
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
-      <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr"/>
@@ -4205,7 +3969,6 @@
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
-      <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr"/>
@@ -4218,7 +3981,6 @@
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr"/>
@@ -4231,7 +3993,6 @@
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr"/>
@@ -4244,7 +4005,6 @@
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
-      <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr"/>
@@ -4257,7 +4017,6 @@
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr"/>
@@ -4270,7 +4029,6 @@
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr"/>
@@ -4283,7 +4041,6 @@
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr"/>
@@ -4296,7 +4053,6 @@
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr"/>
@@ -4309,7 +4065,6 @@
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr"/>
@@ -4322,7 +4077,6 @@
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr"/>
@@ -4335,7 +4089,6 @@
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr"/>
@@ -4348,7 +4101,6 @@
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr"/>
@@ -4361,7 +4113,6 @@
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr"/>
@@ -4374,7 +4125,6 @@
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr"/>
@@ -4387,7 +4137,6 @@
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr"/>
@@ -4400,7 +4149,6 @@
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr"/>
@@ -4413,7 +4161,6 @@
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr"/>
@@ -4426,7 +4173,6 @@
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr"/>
@@ -4439,7 +4185,6 @@
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr"/>
@@ -4452,7 +4197,6 @@
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr"/>
@@ -4465,7 +4209,6 @@
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr"/>
@@ -4478,7 +4221,6 @@
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr"/>
@@ -4491,7 +4233,6 @@
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
-      <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr"/>
@@ -4504,7 +4245,6 @@
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr"/>
-      <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr"/>
@@ -4517,7 +4257,6 @@
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr"/>
@@ -4530,7 +4269,6 @@
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr"/>
-      <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr"/>
@@ -4543,7 +4281,6 @@
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr"/>
-      <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr"/>
@@ -4556,7 +4293,6 @@
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr"/>
-      <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr"/>
@@ -4569,7 +4305,6 @@
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr"/>
-      <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr"/>
@@ -4582,7 +4317,6 @@
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr"/>
-      <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr"/>
@@ -4595,7 +4329,6 @@
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr"/>
@@ -4608,7 +4341,6 @@
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr"/>
@@ -4621,7 +4353,6 @@
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr"/>
-      <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr"/>
@@ -4634,7 +4365,6 @@
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr"/>
-      <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr"/>
@@ -4647,7 +4377,6 @@
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr"/>
-      <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr"/>
@@ -4660,7 +4389,6 @@
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr"/>
-      <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr"/>
@@ -4673,7 +4401,6 @@
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr"/>
-      <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr"/>
@@ -4686,7 +4413,6 @@
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr"/>
@@ -4699,7 +4425,6 @@
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr"/>
@@ -4712,7 +4437,6 @@
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr"/>
@@ -4725,7 +4449,6 @@
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr"/>
@@ -4738,7 +4461,6 @@
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr"/>
@@ -4751,7 +4473,6 @@
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr"/>
@@ -4764,7 +4485,6 @@
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr"/>
@@ -4777,7 +4497,6 @@
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr"/>
-      <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr"/>
@@ -4790,7 +4509,6 @@
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr"/>
-      <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr"/>
@@ -4803,7 +4521,6 @@
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr"/>
@@ -4816,7 +4533,6 @@
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr"/>
-      <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr"/>
@@ -4829,7 +4545,6 @@
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr"/>
-      <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr"/>
@@ -4842,7 +4557,6 @@
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
-      <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr"/>
@@ -4855,7 +4569,6 @@
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr"/>
-      <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr"/>
@@ -4868,7 +4581,6 @@
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr"/>
-      <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr"/>
@@ -4881,7 +4593,6 @@
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr"/>
-      <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr"/>
@@ -4894,7 +4605,6 @@
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr"/>
-      <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr"/>
@@ -4907,7 +4617,6 @@
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr"/>
-      <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr"/>
@@ -4920,7 +4629,6 @@
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
-      <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr"/>
@@ -4933,7 +4641,6 @@
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
-      <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr"/>
@@ -4946,7 +4653,6 @@
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr"/>
-      <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr"/>
@@ -4959,7 +4665,6 @@
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr"/>
-      <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr"/>
@@ -4972,7 +4677,6 @@
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
-      <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr"/>
@@ -4985,7 +4689,6 @@
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr"/>
@@ -4998,7 +4701,6 @@
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr"/>
@@ -5011,7 +4713,6 @@
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr"/>
-      <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr"/>
@@ -5024,7 +4725,6 @@
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr"/>
-      <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr"/>
@@ -5037,7 +4737,6 @@
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
-      <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr"/>
@@ -5050,7 +4749,6 @@
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr"/>
-      <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr"/>
@@ -5063,7 +4761,6 @@
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr"/>
-      <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr"/>
@@ -5076,7 +4773,6 @@
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr"/>
-      <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr"/>
@@ -5089,7 +4785,6 @@
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr"/>
-      <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr"/>
@@ -5102,7 +4797,6 @@
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
-      <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr"/>
@@ -5115,7 +4809,6 @@
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr"/>
-      <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr"/>
@@ -5128,7 +4821,6 @@
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
-      <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr"/>
@@ -5141,7 +4833,6 @@
       <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr"/>
-      <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr"/>
@@ -5154,7 +4845,6 @@
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr"/>
@@ -5167,7 +4857,6 @@
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr"/>
@@ -5180,7 +4869,6 @@
       <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr"/>
       <c r="J328" t="inlineStr"/>
-      <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr"/>
@@ -5193,7 +4881,6 @@
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr"/>
@@ -5206,7 +4893,6 @@
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr"/>
@@ -5219,7 +4905,6 @@
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr"/>
-      <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr"/>
@@ -5232,7 +4917,6 @@
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr"/>
-      <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr"/>
@@ -5245,7 +4929,6 @@
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
-      <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr"/>
@@ -5258,7 +4941,6 @@
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
-      <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr"/>
@@ -5271,7 +4953,6 @@
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr"/>
@@ -5284,7 +4965,6 @@
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr"/>
-      <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr"/>
@@ -5297,7 +4977,6 @@
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr"/>
@@ -5310,7 +4989,6 @@
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr"/>
@@ -5323,7 +5001,6 @@
       <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr"/>
@@ -5336,7 +5013,6 @@
       <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr"/>
       <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr"/>
@@ -5349,7 +5025,6 @@
       <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr"/>
       <c r="J341" t="inlineStr"/>
-      <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr"/>
@@ -5362,7 +5037,6 @@
       <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr"/>
       <c r="J342" t="inlineStr"/>
-      <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr"/>
@@ -5375,7 +5049,6 @@
       <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr"/>
-      <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr"/>
@@ -5388,7 +5061,6 @@
       <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr"/>
       <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr"/>
@@ -5401,7 +5073,6 @@
       <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr"/>
-      <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr"/>
@@ -5414,7 +5085,6 @@
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr"/>
-      <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr"/>
@@ -5427,7 +5097,6 @@
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr"/>
-      <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr"/>
@@ -5440,7 +5109,6 @@
       <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr"/>
-      <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr"/>
@@ -5453,7 +5121,6 @@
       <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr"/>
       <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr"/>
@@ -5466,7 +5133,6 @@
       <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr"/>
@@ -5479,7 +5145,6 @@
       <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr"/>
       <c r="J351" t="inlineStr"/>
-      <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr"/>
@@ -5492,7 +5157,6 @@
       <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr"/>
@@ -5505,7 +5169,6 @@
       <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr"/>
-      <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr"/>
@@ -5518,7 +5181,6 @@
       <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr"/>
-      <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr"/>
@@ -5531,7 +5193,6 @@
       <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr"/>
@@ -5544,7 +5205,6 @@
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr"/>
-      <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr"/>
@@ -5557,7 +5217,6 @@
       <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr"/>
-      <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr"/>
@@ -5570,7 +5229,6 @@
       <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr"/>
       <c r="J358" t="inlineStr"/>
-      <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr"/>
@@ -5583,7 +5241,6 @@
       <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr"/>
       <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr"/>
@@ -5596,7 +5253,6 @@
       <c r="H360" t="inlineStr"/>
       <c r="I360" t="inlineStr"/>
       <c r="J360" t="inlineStr"/>
-      <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr"/>
@@ -5609,7 +5265,6 @@
       <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr"/>
       <c r="J361" t="inlineStr"/>
-      <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr"/>
@@ -5622,7 +5277,6 @@
       <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr"/>
       <c r="J362" t="inlineStr"/>
-      <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr"/>
@@ -5635,7 +5289,6 @@
       <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr"/>
       <c r="J363" t="inlineStr"/>
-      <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr"/>
@@ -5648,7 +5301,6 @@
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr"/>
       <c r="J364" t="inlineStr"/>
-      <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr"/>
@@ -5661,7 +5313,6 @@
       <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr"/>
       <c r="J365" t="inlineStr"/>
-      <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr"/>
@@ -5674,7 +5325,6 @@
       <c r="H366" t="inlineStr"/>
       <c r="I366" t="inlineStr"/>
       <c r="J366" t="inlineStr"/>
-      <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr"/>
@@ -5687,7 +5337,6 @@
       <c r="H367" t="inlineStr"/>
       <c r="I367" t="inlineStr"/>
       <c r="J367" t="inlineStr"/>
-      <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr"/>
@@ -5700,7 +5349,6 @@
       <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr"/>
       <c r="J368" t="inlineStr"/>
-      <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr"/>
@@ -5713,7 +5361,6 @@
       <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr"/>
       <c r="J369" t="inlineStr"/>
-      <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr"/>
@@ -5726,7 +5373,6 @@
       <c r="H370" t="inlineStr"/>
       <c r="I370" t="inlineStr"/>
       <c r="J370" t="inlineStr"/>
-      <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr"/>
@@ -5739,7 +5385,6 @@
       <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr"/>
       <c r="J371" t="inlineStr"/>
-      <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr"/>
@@ -5752,7 +5397,6 @@
       <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr"/>
       <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr"/>
@@ -5765,7 +5409,6 @@
       <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr"/>
       <c r="J373" t="inlineStr"/>
-      <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr"/>
@@ -5778,7 +5421,6 @@
       <c r="H374" t="inlineStr"/>
       <c r="I374" t="inlineStr"/>
       <c r="J374" t="inlineStr"/>
-      <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr"/>
@@ -5791,7 +5433,6 @@
       <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr"/>
       <c r="J375" t="inlineStr"/>
-      <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr"/>
@@ -5804,7 +5445,6 @@
       <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr"/>
       <c r="J376" t="inlineStr"/>
-      <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr"/>
@@ -5817,7 +5457,6 @@
       <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr"/>
       <c r="J377" t="inlineStr"/>
-      <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr"/>
@@ -5830,7 +5469,6 @@
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
-      <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr"/>
@@ -5843,7 +5481,6 @@
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr"/>
       <c r="J379" t="inlineStr"/>
-      <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr"/>
@@ -5856,7 +5493,6 @@
       <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr"/>
       <c r="J380" t="inlineStr"/>
-      <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr"/>
@@ -5869,7 +5505,6 @@
       <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr"/>
       <c r="J381" t="inlineStr"/>
-      <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr"/>
@@ -5882,7 +5517,6 @@
       <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr"/>
       <c r="J382" t="inlineStr"/>
-      <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr"/>
@@ -5895,7 +5529,6 @@
       <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr"/>
       <c r="J383" t="inlineStr"/>
-      <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr"/>
@@ -5908,7 +5541,6 @@
       <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr"/>
       <c r="J384" t="inlineStr"/>
-      <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr"/>
@@ -5921,7 +5553,6 @@
       <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr"/>
       <c r="J385" t="inlineStr"/>
-      <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr"/>
@@ -5934,7 +5565,6 @@
       <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr"/>
-      <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr"/>
@@ -5947,7 +5577,6 @@
       <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr"/>
-      <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr"/>
@@ -5960,7 +5589,6 @@
       <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr"/>
       <c r="J388" t="inlineStr"/>
-      <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr"/>
@@ -5973,7 +5601,6 @@
       <c r="H389" t="inlineStr"/>
       <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr"/>
-      <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr"/>
@@ -5986,7 +5613,6 @@
       <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr"/>
       <c r="J390" t="inlineStr"/>
-      <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr"/>
@@ -5999,7 +5625,6 @@
       <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr"/>
       <c r="J391" t="inlineStr"/>
-      <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr"/>
@@ -6012,7 +5637,6 @@
       <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr"/>
       <c r="J392" t="inlineStr"/>
-      <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr"/>
@@ -6025,7 +5649,6 @@
       <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr"/>
       <c r="J393" t="inlineStr"/>
-      <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr"/>
@@ -6038,7 +5661,6 @@
       <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr"/>
       <c r="J394" t="inlineStr"/>
-      <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr"/>
@@ -6051,7 +5673,6 @@
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr"/>
       <c r="J395" t="inlineStr"/>
-      <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr"/>
@@ -6064,7 +5685,6 @@
       <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr"/>
       <c r="J396" t="inlineStr"/>
-      <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr"/>
@@ -6077,7 +5697,6 @@
       <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr"/>
       <c r="J397" t="inlineStr"/>
-      <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr"/>
@@ -6090,7 +5709,6 @@
       <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr"/>
       <c r="J398" t="inlineStr"/>
-      <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr"/>
@@ -6103,7 +5721,6 @@
       <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr"/>
       <c r="J399" t="inlineStr"/>
-      <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr"/>
@@ -6116,7 +5733,6 @@
       <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr"/>
-      <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr"/>
@@ -6129,7 +5745,6 @@
       <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr"/>
-      <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr"/>
@@ -6142,7 +5757,6 @@
       <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr"/>
       <c r="J402" t="inlineStr"/>
-      <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr"/>
@@ -6155,7 +5769,6 @@
       <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr"/>
       <c r="J403" t="inlineStr"/>
-      <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr"/>
@@ -6168,7 +5781,6 @@
       <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr"/>
       <c r="J404" t="inlineStr"/>
-      <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr"/>
@@ -6181,7 +5793,6 @@
       <c r="H405" t="inlineStr"/>
       <c r="I405" t="inlineStr"/>
       <c r="J405" t="inlineStr"/>
-      <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr"/>
@@ -6194,7 +5805,6 @@
       <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr"/>
       <c r="J406" t="inlineStr"/>
-      <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr"/>
@@ -6207,7 +5817,6 @@
       <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr"/>
       <c r="J407" t="inlineStr"/>
-      <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr"/>
@@ -6220,7 +5829,6 @@
       <c r="H408" t="inlineStr"/>
       <c r="I408" t="inlineStr"/>
       <c r="J408" t="inlineStr"/>
-      <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr"/>
@@ -6233,7 +5841,6 @@
       <c r="H409" t="inlineStr"/>
       <c r="I409" t="inlineStr"/>
       <c r="J409" t="inlineStr"/>
-      <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr"/>
@@ -6246,7 +5853,6 @@
       <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr"/>
       <c r="J410" t="inlineStr"/>
-      <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr"/>
@@ -6259,7 +5865,6 @@
       <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr"/>
       <c r="J411" t="inlineStr"/>
-      <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr"/>
@@ -6272,7 +5877,6 @@
       <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr"/>
       <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr"/>
@@ -6285,7 +5889,6 @@
       <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr"/>
       <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr"/>
@@ -6298,7 +5901,6 @@
       <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr"/>
       <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr"/>
@@ -6311,7 +5913,6 @@
       <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr"/>
       <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr"/>
@@ -6324,7 +5925,6 @@
       <c r="H416" t="inlineStr"/>
       <c r="I416" t="inlineStr"/>
       <c r="J416" t="inlineStr"/>
-      <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr"/>
@@ -6337,7 +5937,6 @@
       <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr"/>
       <c r="J417" t="inlineStr"/>
-      <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr"/>
@@ -6350,7 +5949,6 @@
       <c r="H418" t="inlineStr"/>
       <c r="I418" t="inlineStr"/>
       <c r="J418" t="inlineStr"/>
-      <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr"/>
@@ -6363,7 +5961,6 @@
       <c r="H419" t="inlineStr"/>
       <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr"/>
-      <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr"/>
@@ -6376,7 +5973,6 @@
       <c r="H420" t="inlineStr"/>
       <c r="I420" t="inlineStr"/>
       <c r="J420" t="inlineStr"/>
-      <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr"/>
@@ -6389,7 +5985,6 @@
       <c r="H421" t="inlineStr"/>
       <c r="I421" t="inlineStr"/>
       <c r="J421" t="inlineStr"/>
-      <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr"/>
@@ -6402,7 +5997,6 @@
       <c r="H422" t="inlineStr"/>
       <c r="I422" t="inlineStr"/>
       <c r="J422" t="inlineStr"/>
-      <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr"/>
@@ -6415,7 +6009,6 @@
       <c r="H423" t="inlineStr"/>
       <c r="I423" t="inlineStr"/>
       <c r="J423" t="inlineStr"/>
-      <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr"/>
@@ -6428,7 +6021,6 @@
       <c r="H424" t="inlineStr"/>
       <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr"/>
-      <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr"/>
@@ -6441,7 +6033,6 @@
       <c r="H425" t="inlineStr"/>
       <c r="I425" t="inlineStr"/>
       <c r="J425" t="inlineStr"/>
-      <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr"/>
@@ -6454,7 +6045,6 @@
       <c r="H426" t="inlineStr"/>
       <c r="I426" t="inlineStr"/>
       <c r="J426" t="inlineStr"/>
-      <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr"/>
@@ -6467,7 +6057,6 @@
       <c r="H427" t="inlineStr"/>
       <c r="I427" t="inlineStr"/>
       <c r="J427" t="inlineStr"/>
-      <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr"/>
@@ -6480,7 +6069,6 @@
       <c r="H428" t="inlineStr"/>
       <c r="I428" t="inlineStr"/>
       <c r="J428" t="inlineStr"/>
-      <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr"/>
@@ -6493,7 +6081,6 @@
       <c r="H429" t="inlineStr"/>
       <c r="I429" t="inlineStr"/>
       <c r="J429" t="inlineStr"/>
-      <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr"/>
@@ -6506,7 +6093,6 @@
       <c r="H430" t="inlineStr"/>
       <c r="I430" t="inlineStr"/>
       <c r="J430" t="inlineStr"/>
-      <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr"/>
@@ -6519,7 +6105,6 @@
       <c r="H431" t="inlineStr"/>
       <c r="I431" t="inlineStr"/>
       <c r="J431" t="inlineStr"/>
-      <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr"/>
@@ -6532,7 +6117,6 @@
       <c r="H432" t="inlineStr"/>
       <c r="I432" t="inlineStr"/>
       <c r="J432" t="inlineStr"/>
-      <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr"/>
@@ -6545,7 +6129,6 @@
       <c r="H433" t="inlineStr"/>
       <c r="I433" t="inlineStr"/>
       <c r="J433" t="inlineStr"/>
-      <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr"/>
@@ -6558,7 +6141,6 @@
       <c r="H434" t="inlineStr"/>
       <c r="I434" t="inlineStr"/>
       <c r="J434" t="inlineStr"/>
-      <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr"/>
@@ -6571,7 +6153,6 @@
       <c r="H435" t="inlineStr"/>
       <c r="I435" t="inlineStr"/>
       <c r="J435" t="inlineStr"/>
-      <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr"/>
@@ -6584,7 +6165,6 @@
       <c r="H436" t="inlineStr"/>
       <c r="I436" t="inlineStr"/>
       <c r="J436" t="inlineStr"/>
-      <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr"/>
@@ -6597,7 +6177,6 @@
       <c r="H437" t="inlineStr"/>
       <c r="I437" t="inlineStr"/>
       <c r="J437" t="inlineStr"/>
-      <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr"/>
@@ -6610,7 +6189,6 @@
       <c r="H438" t="inlineStr"/>
       <c r="I438" t="inlineStr"/>
       <c r="J438" t="inlineStr"/>
-      <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr"/>
@@ -6623,7 +6201,6 @@
       <c r="H439" t="inlineStr"/>
       <c r="I439" t="inlineStr"/>
       <c r="J439" t="inlineStr"/>
-      <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr"/>
@@ -6636,7 +6213,6 @@
       <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr"/>
       <c r="J440" t="inlineStr"/>
-      <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr"/>
@@ -6649,7 +6225,6 @@
       <c r="H441" t="inlineStr"/>
       <c r="I441" t="inlineStr"/>
       <c r="J441" t="inlineStr"/>
-      <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr"/>
@@ -6662,7 +6237,6 @@
       <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr"/>
       <c r="J442" t="inlineStr"/>
-      <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr"/>
@@ -6675,7 +6249,6 @@
       <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr"/>
       <c r="J443" t="inlineStr"/>
-      <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr"/>
@@ -6688,7 +6261,6 @@
       <c r="H444" t="inlineStr"/>
       <c r="I444" t="inlineStr"/>
       <c r="J444" t="inlineStr"/>
-      <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr"/>
@@ -6701,7 +6273,6 @@
       <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr"/>
       <c r="J445" t="inlineStr"/>
-      <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr"/>
@@ -6714,7 +6285,6 @@
       <c r="H446" t="inlineStr"/>
       <c r="I446" t="inlineStr"/>
       <c r="J446" t="inlineStr"/>
-      <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr"/>
@@ -6727,7 +6297,6 @@
       <c r="H447" t="inlineStr"/>
       <c r="I447" t="inlineStr"/>
       <c r="J447" t="inlineStr"/>
-      <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr"/>
@@ -6740,7 +6309,6 @@
       <c r="H448" t="inlineStr"/>
       <c r="I448" t="inlineStr"/>
       <c r="J448" t="inlineStr"/>
-      <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr"/>
@@ -6753,7 +6321,6 @@
       <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr"/>
-      <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr"/>
@@ -6766,7 +6333,6 @@
       <c r="H450" t="inlineStr"/>
       <c r="I450" t="inlineStr"/>
       <c r="J450" t="inlineStr"/>
-      <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr"/>
@@ -6779,7 +6345,6 @@
       <c r="H451" t="inlineStr"/>
       <c r="I451" t="inlineStr"/>
       <c r="J451" t="inlineStr"/>
-      <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr"/>
@@ -6792,7 +6357,6 @@
       <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr"/>
       <c r="J452" t="inlineStr"/>
-      <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr"/>
@@ -6805,7 +6369,6 @@
       <c r="H453" t="inlineStr"/>
       <c r="I453" t="inlineStr"/>
       <c r="J453" t="inlineStr"/>
-      <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr"/>
@@ -6818,7 +6381,6 @@
       <c r="H454" t="inlineStr"/>
       <c r="I454" t="inlineStr"/>
       <c r="J454" t="inlineStr"/>
-      <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr"/>
@@ -6831,7 +6393,6 @@
       <c r="H455" t="inlineStr"/>
       <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr"/>
-      <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr"/>
@@ -6844,7 +6405,6 @@
       <c r="H456" t="inlineStr"/>
       <c r="I456" t="inlineStr"/>
       <c r="J456" t="inlineStr"/>
-      <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr"/>
@@ -6857,7 +6417,6 @@
       <c r="H457" t="inlineStr"/>
       <c r="I457" t="inlineStr"/>
       <c r="J457" t="inlineStr"/>
-      <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr"/>
@@ -6870,7 +6429,6 @@
       <c r="H458" t="inlineStr"/>
       <c r="I458" t="inlineStr"/>
       <c r="J458" t="inlineStr"/>
-      <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr"/>
@@ -6883,7 +6441,6 @@
       <c r="H459" t="inlineStr"/>
       <c r="I459" t="inlineStr"/>
       <c r="J459" t="inlineStr"/>
-      <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr"/>
@@ -6896,7 +6453,6 @@
       <c r="H460" t="inlineStr"/>
       <c r="I460" t="inlineStr"/>
       <c r="J460" t="inlineStr"/>
-      <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr"/>
@@ -6909,7 +6465,6 @@
       <c r="H461" t="inlineStr"/>
       <c r="I461" t="inlineStr"/>
       <c r="J461" t="inlineStr"/>
-      <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr"/>
@@ -6922,7 +6477,6 @@
       <c r="H462" t="inlineStr"/>
       <c r="I462" t="inlineStr"/>
       <c r="J462" t="inlineStr"/>
-      <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr"/>
@@ -6935,7 +6489,6 @@
       <c r="H463" t="inlineStr"/>
       <c r="I463" t="inlineStr"/>
       <c r="J463" t="inlineStr"/>
-      <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr"/>
@@ -6948,7 +6501,6 @@
       <c r="H464" t="inlineStr"/>
       <c r="I464" t="inlineStr"/>
       <c r="J464" t="inlineStr"/>
-      <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr"/>
@@ -6961,7 +6513,6 @@
       <c r="H465" t="inlineStr"/>
       <c r="I465" t="inlineStr"/>
       <c r="J465" t="inlineStr"/>
-      <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr"/>
@@ -6974,7 +6525,6 @@
       <c r="H466" t="inlineStr"/>
       <c r="I466" t="inlineStr"/>
       <c r="J466" t="inlineStr"/>
-      <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr"/>
@@ -6987,7 +6537,6 @@
       <c r="H467" t="inlineStr"/>
       <c r="I467" t="inlineStr"/>
       <c r="J467" t="inlineStr"/>
-      <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr"/>
@@ -7000,7 +6549,6 @@
       <c r="H468" t="inlineStr"/>
       <c r="I468" t="inlineStr"/>
       <c r="J468" t="inlineStr"/>
-      <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr"/>
@@ -7013,7 +6561,6 @@
       <c r="H469" t="inlineStr"/>
       <c r="I469" t="inlineStr"/>
       <c r="J469" t="inlineStr"/>
-      <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr"/>
@@ -7026,7 +6573,6 @@
       <c r="H470" t="inlineStr"/>
       <c r="I470" t="inlineStr"/>
       <c r="J470" t="inlineStr"/>
-      <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr"/>
@@ -7039,7 +6585,6 @@
       <c r="H471" t="inlineStr"/>
       <c r="I471" t="inlineStr"/>
       <c r="J471" t="inlineStr"/>
-      <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr"/>
@@ -7052,7 +6597,6 @@
       <c r="H472" t="inlineStr"/>
       <c r="I472" t="inlineStr"/>
       <c r="J472" t="inlineStr"/>
-      <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr"/>
@@ -7065,7 +6609,6 @@
       <c r="H473" t="inlineStr"/>
       <c r="I473" t="inlineStr"/>
       <c r="J473" t="inlineStr"/>
-      <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr"/>
@@ -7078,7 +6621,6 @@
       <c r="H474" t="inlineStr"/>
       <c r="I474" t="inlineStr"/>
       <c r="J474" t="inlineStr"/>
-      <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr"/>
@@ -7091,7 +6633,6 @@
       <c r="H475" t="inlineStr"/>
       <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr"/>
-      <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr"/>
@@ -7104,7 +6645,6 @@
       <c r="H476" t="inlineStr"/>
       <c r="I476" t="inlineStr"/>
       <c r="J476" t="inlineStr"/>
-      <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr"/>
@@ -7117,7 +6657,6 @@
       <c r="H477" t="inlineStr"/>
       <c r="I477" t="inlineStr"/>
       <c r="J477" t="inlineStr"/>
-      <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr"/>
@@ -7130,7 +6669,6 @@
       <c r="H478" t="inlineStr"/>
       <c r="I478" t="inlineStr"/>
       <c r="J478" t="inlineStr"/>
-      <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr"/>
@@ -7143,7 +6681,6 @@
       <c r="H479" t="inlineStr"/>
       <c r="I479" t="inlineStr"/>
       <c r="J479" t="inlineStr"/>
-      <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr"/>
@@ -7156,7 +6693,6 @@
       <c r="H480" t="inlineStr"/>
       <c r="I480" t="inlineStr"/>
       <c r="J480" t="inlineStr"/>
-      <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr"/>
@@ -7169,7 +6705,6 @@
       <c r="H481" t="inlineStr"/>
       <c r="I481" t="inlineStr"/>
       <c r="J481" t="inlineStr"/>
-      <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr"/>
@@ -7182,7 +6717,6 @@
       <c r="H482" t="inlineStr"/>
       <c r="I482" t="inlineStr"/>
       <c r="J482" t="inlineStr"/>
-      <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr"/>
@@ -7195,7 +6729,6 @@
       <c r="H483" t="inlineStr"/>
       <c r="I483" t="inlineStr"/>
       <c r="J483" t="inlineStr"/>
-      <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr"/>
@@ -7208,7 +6741,6 @@
       <c r="H484" t="inlineStr"/>
       <c r="I484" t="inlineStr"/>
       <c r="J484" t="inlineStr"/>
-      <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr"/>
@@ -7221,7 +6753,6 @@
       <c r="H485" t="inlineStr"/>
       <c r="I485" t="inlineStr"/>
       <c r="J485" t="inlineStr"/>
-      <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr"/>
@@ -7234,7 +6765,6 @@
       <c r="H486" t="inlineStr"/>
       <c r="I486" t="inlineStr"/>
       <c r="J486" t="inlineStr"/>
-      <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr"/>
@@ -7247,7 +6777,6 @@
       <c r="H487" t="inlineStr"/>
       <c r="I487" t="inlineStr"/>
       <c r="J487" t="inlineStr"/>
-      <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr"/>
@@ -7260,7 +6789,6 @@
       <c r="H488" t="inlineStr"/>
       <c r="I488" t="inlineStr"/>
       <c r="J488" t="inlineStr"/>
-      <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr"/>
@@ -7273,7 +6801,6 @@
       <c r="H489" t="inlineStr"/>
       <c r="I489" t="inlineStr"/>
       <c r="J489" t="inlineStr"/>
-      <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr"/>
@@ -7286,7 +6813,6 @@
       <c r="H490" t="inlineStr"/>
       <c r="I490" t="inlineStr"/>
       <c r="J490" t="inlineStr"/>
-      <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr"/>
@@ -7299,7 +6825,6 @@
       <c r="H491" t="inlineStr"/>
       <c r="I491" t="inlineStr"/>
       <c r="J491" t="inlineStr"/>
-      <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr"/>
@@ -7312,7 +6837,6 @@
       <c r="H492" t="inlineStr"/>
       <c r="I492" t="inlineStr"/>
       <c r="J492" t="inlineStr"/>
-      <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr"/>
@@ -7325,7 +6849,6 @@
       <c r="H493" t="inlineStr"/>
       <c r="I493" t="inlineStr"/>
       <c r="J493" t="inlineStr"/>
-      <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr"/>
@@ -7338,7 +6861,6 @@
       <c r="H494" t="inlineStr"/>
       <c r="I494" t="inlineStr"/>
       <c r="J494" t="inlineStr"/>
-      <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr"/>
@@ -7351,7 +6873,6 @@
       <c r="H495" t="inlineStr"/>
       <c r="I495" t="inlineStr"/>
       <c r="J495" t="inlineStr"/>
-      <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr"/>
@@ -7364,7 +6885,6 @@
       <c r="H496" t="inlineStr"/>
       <c r="I496" t="inlineStr"/>
       <c r="J496" t="inlineStr"/>
-      <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr"/>
@@ -7377,7 +6897,6 @@
       <c r="H497" t="inlineStr"/>
       <c r="I497" t="inlineStr"/>
       <c r="J497" t="inlineStr"/>
-      <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr"/>
@@ -7390,7 +6909,6 @@
       <c r="H498" t="inlineStr"/>
       <c r="I498" t="inlineStr"/>
       <c r="J498" t="inlineStr"/>
-      <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr"/>
@@ -7403,7 +6921,6 @@
       <c r="H499" t="inlineStr"/>
       <c r="I499" t="inlineStr"/>
       <c r="J499" t="inlineStr"/>
-      <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr"/>
@@ -7416,7 +6933,6 @@
       <c r="H500" t="inlineStr"/>
       <c r="I500" t="inlineStr"/>
       <c r="J500" t="inlineStr"/>
-      <c r="K500" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7432,14 +6948,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -7467,24 +6982,19 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
           <t>Ext.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <f>SORT(FILTER({{'Staff Directory'!B2:B,'Staff Directory'!A2:A,'Staff Directory'!E2:E,'Staff Directory'!G2:G,'Staff Directory'!I2:I}},'Staff Directory'!D2:D&lt;&gt;"",'Staff Directory'!B2:B&lt;&gt;""),4,TRUE,1,TRUE)</f>
+        <f>SORT(FILTER({{'Staff Directory'!B2:B,'Staff Directory'!A2:A,'Staff Directory'!E2:E,'Staff Directory'!H2:H}},'Staff Directory'!D2:D&lt;&gt;"",'Staff Directory'!B2:B&lt;&gt;""),1,TRUE)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
